--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/tarapaca.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/tarapaca.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarapacá" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tarapacá" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>628-440-CM25</t>
+          <t>3447-126-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,32 +554,28 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>XERTICA CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.223.453-8</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>94180.98</v>
+        <v>66347.45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>628-483-CM25</t>
+          <t>3447-308-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -604,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -619,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -634,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>21145.11</v>
+        <v>8620.549999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>628-490-CM25</t>
+          <t>3885-140-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -650,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -665,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -680,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -695,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>6678.28</v>
+        <v>7672.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3447-162-CM26</t>
+          <t>3885-139-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -711,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -741,32 +737,28 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>84469.77</v>
+        <v>7672.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1026727-66-CM26</t>
+          <t>907562-83-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -776,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -791,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>65.154.398-3</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -806,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -821,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3827.04</v>
+        <v>8433.530000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2404-577-CM26</t>
+          <t>2404-608-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -837,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -867,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -882,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>34026.38</v>
+        <v>66383.56</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3885-205-CM26</t>
+          <t>3352-208-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -898,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -913,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -928,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -943,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>8255.860000000001</v>
+        <v>1057.55</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3885-206-CM26</t>
+          <t>768-483-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -959,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -974,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>72.223.100-7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>GOBIERNO REGIONAL DE TARAPACA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -989,28 +981,32 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>8255.860000000001</v>
+        <v>89853.71000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>907562-59-CM26</t>
+          <t>1055513-3-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1020,12 +1016,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1035,12 +1031,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>60.511.010-K</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1050,12 +1046,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1065,13 +1061,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8426.75</v>
+        <v>2749.17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>722640-63-CM26</t>
+          <t>2404-1413-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1081,27 +1077,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.250.400-3</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLCHANE</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1111,12 +1107,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>NextTime Software S.A.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>99.576.370-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1126,6 +1122,685 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
+        <v>21302.19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2404-1412-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>69.010.300-1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MSLI Latam Inc.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>39184.32</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>628-483-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>60.107.000-6</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>21145.11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>628-490-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>60.107.000-6</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>6678.28</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>628-440-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>60.107.000-6</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>XERTICA CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>77.223.453-8</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>94180.98</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3447-162-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.265.100-6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>CLOUDLATAM SPA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>84469.77</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1026727-66-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>65.154.398-3</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Inversiones Hebo Limitada</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>3827.04</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2404-577-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>69.010.300-1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>34026.38</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3885-205-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69.010.400-8</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PICA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>8255.860000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3885-206-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>69.010.400-8</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PICA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>8255.860000000001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>907562-59-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>69.010.400-8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PICA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>8426.75</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>722640-63-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>69.250.400-3</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COLCHANE</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
         <v>4435.13</v>
       </c>
     </row>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/tarapaca.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -758,7 +758,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>907562-83-CM25</t>
+          <t>2404-608-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -778,17 +778,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8433.530000000001</v>
+        <v>66383.56</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2404-608-CM25</t>
+          <t>907562-83-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -839,17 +839,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>66383.56</v>
+        <v>8433.530000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1189,7 +1189,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>628-483-CM25</t>
+          <t>1305552-147-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1214,12 +1214,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>61.981.030-9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>21145.11</v>
+        <v>2548.69</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>628-490-CM25</t>
+          <t>3447-162-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1290,28 +1290,32 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>6678.28</v>
+        <v>84469.77</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>628-440-CM25</t>
+          <t>1026727-66-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1321,12 +1325,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1336,12 +1340,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>65.154.398-3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1351,32 +1355,28 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>XERTICA CHILE SPA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.223.453-8</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>94180.98</v>
+        <v>3827.04</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3447-162-CM26</t>
+          <t>2404-577-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1386,27 +1386,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1416,32 +1416,28 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>84469.77</v>
+        <v>34026.38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1026727-66-CM26</t>
+          <t>3885-205-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1451,12 +1447,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1466,12 +1462,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>65.154.398-3</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1481,12 +1477,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1496,13 +1492,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3827.04</v>
+        <v>8255.860000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2404-577-CM26</t>
+          <t>3885-206-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1517,22 +1513,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1542,12 +1538,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1557,13 +1553,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>34026.38</v>
+        <v>8255.860000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3885-205-CM26</t>
+          <t>907562-59-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1578,7 +1574,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1618,13 +1614,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>8255.860000000001</v>
+        <v>8426.75</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3885-206-CM26</t>
+          <t>722640-63-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1634,12 +1630,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1649,12 +1645,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>69.250.400-3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>I MUNICIPALIDAD DE COLCHANE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1679,13 +1675,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>8255.860000000001</v>
+        <v>4435.13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>907562-59-CM26</t>
+          <t>1057448-421-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1695,27 +1691,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1725,12 +1721,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1740,68 +1736,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>8426.75</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>722640-63-CM26</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>69.250.400-3</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE COLCHANE</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>TECNOLOGIA BS SPA</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>4435.13</v>
+        <v>8979.690000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/tarapaca.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/tarapaca.xlsx
@@ -562,7 +562,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1054,7 +1082,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1237,7 +1269,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1363,7 +1399,11 @@
           <t>77.553.790-6</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1424,7 +1464,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1485,7 +1529,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1546,7 +1594,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1607,7 +1659,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1668,7 +1724,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1729,7 +1789,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/tarapaca.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -774,7 +774,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2404-608-CM25</t>
+          <t>907562-83-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -814,17 +814,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>66383.56</v>
+        <v>8433.530000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>907562-83-CM25</t>
+          <t>2404-608-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -859,17 +859,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>8433.530000000001</v>
+        <v>66383.56</v>
       </c>
     </row>
     <row r="8">
@@ -1801,6 +1801,71 @@
       </c>
       <c r="M21" s="2" t="n">
         <v>8979.690000000001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2404-1169-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>69.010.300-1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>20673.87</v>
       </c>
     </row>
   </sheetData>
